--- a/inventories/optimized/lci-Sal-de-Vida.xlsx
+++ b/inventories/optimized/lci-Sal-de-Vida.xlsx
@@ -832,7 +832,7 @@
         <v>29</v>
       </c>
       <c r="B28">
-        <v>0.9999980775808083</v>
+        <v>0.9999980775808084</v>
       </c>
       <c r="C28" t="s">
         <v>1</v>
@@ -849,7 +849,7 @@
         <v>30</v>
       </c>
       <c r="B29">
-        <v>0.2569229089269826</v>
+        <v>0.2569229089269827</v>
       </c>
       <c r="C29" t="s">
         <v>1</v>
@@ -866,7 +866,7 @@
         <v>31</v>
       </c>
       <c r="B30">
-        <v>2.873513257570379E-07</v>
+        <v>2.87351325757038E-07</v>
       </c>
       <c r="C30" t="s">
         <v>32</v>
@@ -900,7 +900,7 @@
         <v>34</v>
       </c>
       <c r="B32">
-        <v>-1.075256499112653E-06</v>
+        <v>-1.075256499112652E-06</v>
       </c>
       <c r="C32" t="s">
         <v>35</v>
@@ -1164,7 +1164,7 @@
         <v>3</v>
       </c>
       <c r="B58">
-        <v>0.5911111721492136</v>
+        <v>0.5843705555292796</v>
       </c>
       <c r="C58" t="s">
         <v>1</v>
@@ -1181,7 +1181,7 @@
         <v>39</v>
       </c>
       <c r="B59">
-        <v>0.261111034813483</v>
+        <v>0.2695368055884005</v>
       </c>
       <c r="C59" t="s">
         <v>1</v>
@@ -1198,7 +1198,7 @@
         <v>30</v>
       </c>
       <c r="B60">
-        <v>0.06407637926953313</v>
+        <v>0.06614405474788825</v>
       </c>
       <c r="C60" t="s">
         <v>1</v>
@@ -1215,7 +1215,7 @@
         <v>31</v>
       </c>
       <c r="B61">
-        <v>0.1477777930373034</v>
+        <v>0.1460926388823199</v>
       </c>
       <c r="C61" t="s">
         <v>32</v>
@@ -1330,7 +1330,7 @@
         <v>3</v>
       </c>
       <c r="B73">
-        <v>0.0259785248516498</v>
+        <v>0.02597852485164981</v>
       </c>
       <c r="C73" t="s">
         <v>1</v>
@@ -1381,7 +1381,7 @@
         <v>31</v>
       </c>
       <c r="B76">
-        <v>0.00649463121291245</v>
+        <v>0.006494631212912451</v>
       </c>
       <c r="C76" t="s">
         <v>32</v>
@@ -1645,7 +1645,7 @@
         <v>38</v>
       </c>
       <c r="B102">
-        <v>6.471163166016302</v>
+        <v>6.545806950810774</v>
       </c>
       <c r="C102" t="s">
         <v>1</v>
@@ -1662,7 +1662,7 @@
         <v>22</v>
       </c>
       <c r="B103">
-        <v>0.006277994116284471</v>
+        <v>0.006350409728398513</v>
       </c>
       <c r="C103" t="s">
         <v>23</v>
@@ -1679,7 +1679,7 @@
         <v>42</v>
       </c>
       <c r="B104">
-        <v>-0.005471163166016302</v>
+        <v>-0.005545806950810774</v>
       </c>
       <c r="C104" t="s">
         <v>1</v>
@@ -2224,7 +2224,7 @@
         <v>48</v>
       </c>
       <c r="B157">
-        <v>0.02428571428176039</v>
+        <v>0.02325825820889415</v>
       </c>
       <c r="D157" t="s">
         <v>11</v>
@@ -2241,7 +2241,7 @@
         <v>49</v>
       </c>
       <c r="B158">
-        <v>9.539237644514692E-11</v>
+        <v>9.135660976574894E-11</v>
       </c>
       <c r="D158" t="s">
         <v>50</v>
@@ -2258,7 +2258,7 @@
         <v>52</v>
       </c>
       <c r="B159">
-        <v>2.384809411128673E-12</v>
+        <v>2.283915244143724E-12</v>
       </c>
       <c r="D159" t="s">
         <v>53</v>
@@ -2275,7 +2275,7 @@
         <v>54</v>
       </c>
       <c r="B160">
-        <v>2.384809411128673E-12</v>
+        <v>2.283915244143724E-12</v>
       </c>
       <c r="D160" t="s">
         <v>53</v>
@@ -2326,7 +2326,7 @@
         <v>3</v>
       </c>
       <c r="B163">
-        <v>0.08195918802077415</v>
+        <v>0.1207987542144489</v>
       </c>
       <c r="C163" t="s">
         <v>1</v>
@@ -2343,7 +2343,7 @@
         <v>55</v>
       </c>
       <c r="B164">
-        <v>6.627424484057881E-05</v>
+        <v>6.347037938510741E-05</v>
       </c>
       <c r="C164" t="s">
         <v>1</v>
@@ -2360,7 +2360,7 @@
         <v>22</v>
       </c>
       <c r="B165">
-        <v>0.02687844971310444</v>
+        <v>0.02574496339120929</v>
       </c>
       <c r="C165" t="s">
         <v>23</v>
@@ -2377,7 +2377,7 @@
         <v>57</v>
       </c>
       <c r="B166">
-        <v>5.068040009424847E-10</v>
+        <v>0.131697756877103</v>
       </c>
       <c r="C166" t="s">
         <v>35</v>
@@ -2394,7 +2394,7 @@
         <v>58</v>
       </c>
       <c r="B167">
-        <v>0.0001475265381443402</v>
+        <v>0.0001412851307158103</v>
       </c>
       <c r="C167" t="s">
         <v>35</v>
@@ -2411,7 +2411,7 @@
         <v>59</v>
       </c>
       <c r="B168">
-        <v>-7.56866287236478E-17</v>
+        <v>-7.248455340419597E-17</v>
       </c>
       <c r="C168" t="s">
         <v>35</v>
@@ -2428,7 +2428,7 @@
         <v>42</v>
       </c>
       <c r="B169">
-        <v>-8.195918785796678E-05</v>
+        <v>-7.849173928656128E-05</v>
       </c>
       <c r="C169" t="s">
         <v>1</v>
@@ -2526,7 +2526,7 @@
         <v>60</v>
       </c>
       <c r="B180">
-        <v>-0.0006900000000000001</v>
+        <v>-0.00069</v>
       </c>
       <c r="D180" t="s">
         <v>11</v>
